--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/NEBRASKA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/NEBRASKA_2015.xlsx
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C83">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C122">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C201">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C526">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C537">
